--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 днрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 днрсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253ACCD0-F285-4F9F-A7A9-B0192EE8E81F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5485DE-FE1F-458A-B42D-6C4119A3ED8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -151,6 +148,12 @@
   </si>
   <si>
     <t>нужно увеличить продажи</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>20,07,</t>
   </si>
 </sst>
 </file>
@@ -746,25 +749,25 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -809,19 +812,21 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -895,7 +900,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -910,7 +915,7 @@
       <c r="V5" s="1"/>
       <c r="W5" s="4">
         <f>SUM(W6:W500)</f>
-        <v>117.05</v>
+        <v>120</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -941,10 +946,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
         <v>162</v>
@@ -963,7 +968,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -996,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W6" s="1">
         <f t="shared" ref="W6:W16" si="2">G6*Q6</f>
@@ -1031,10 +1036,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
         <v>47.396999999999998</v>
@@ -1051,7 +1056,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1086,7 +1091,7 @@
         <v>0.91639999999999999</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
@@ -1121,10 +1126,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
         <v>113.04600000000001</v>
@@ -1143,7 +1148,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1176,7 +1181,7 @@
         <v>0.90839999999999999</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" si="2"/>
@@ -1211,10 +1216,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1">
         <v>191</v>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1266,7 +1271,7 @@
         <v>2.4</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="2"/>
@@ -1301,10 +1306,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1">
         <v>160</v>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1391,10 +1396,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>144</v>
@@ -1413,7 +1418,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1433,12 +1438,11 @@
         <v>20.2</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q7:Q16" si="6">15*P11-O11-F11</f>
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.099009900990099</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
@@ -1453,7 +1457,7 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1">
         <f t="shared" si="2"/>
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -1484,10 +1488,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>158</v>
@@ -1506,7 +1510,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1576,10 +1580,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
         <v>149</v>
@@ -1598,7 +1602,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1616,12 +1620,11 @@
         <v>13.8</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="6"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.144927536231883</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="5"/>
@@ -1636,7 +1639,7 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1">
         <f t="shared" si="2"/>
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
@@ -1667,10 +1670,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
         <v>239</v>
@@ -1687,7 +1690,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1705,12 +1708,11 @@
         <v>14.2</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="6"/>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.352112676056338</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
@@ -1725,7 +1727,7 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1">
         <f t="shared" si="2"/>
-        <v>15.749999999999998</v>
+        <v>17.5</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -1756,10 +1758,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1">
         <v>208</v>
@@ -1778,7 +1780,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1811,7 +1813,7 @@
         <v>1.6</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="2"/>
@@ -1846,10 +1848,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1">
         <v>397</v>
@@ -1868,7 +1870,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1901,7 +1903,7 @@
         <v>6.2</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" si="2"/>
